--- a/12608016.xlsx
+++ b/12608016.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd440dd7f90bf0f9/Desktop/demo/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F21CB544-8A65-4282-83F0-A0FD9CC9A83E}"/>
+  <xr:revisionPtr revIDLastSave="450" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03551E6D-E1B0-4AEB-A49D-CB84B4C0145E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -270,6 +270,54 @@
   <si>
     <t>performed well in both CA</t>
   </si>
+  <si>
+    <t>tried to study but couldn't focus much</t>
+  </si>
+  <si>
+    <t>very hectic day!</t>
+  </si>
+  <si>
+    <t>went out with friends and had a lot of fun after so many day</t>
+  </si>
+  <si>
+    <t>been feeling tired so took a rest</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>had a lots of junk food today</t>
+  </si>
+  <si>
+    <t>got my favorite MAC lipstick and new outfits as a gift so I'm feeling great today!</t>
+  </si>
+  <si>
+    <t>not a very productive kind of a day</t>
+  </si>
+  <si>
+    <t>studied till midnight for CA-2 of DBMS</t>
+  </si>
+  <si>
+    <t>gave python CA and scored 40/50</t>
+  </si>
+  <si>
+    <t>did good at subjective test but  not satisfied with my viva</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>feeling completely exhausted!</t>
+  </si>
+  <si>
+    <t>took a lot of rest today</t>
+  </si>
+  <si>
+    <t>excited for the weekends</t>
+  </si>
+  <si>
+    <t>had a lot of fun with my sister and explore campus as well</t>
+  </si>
 </sst>
 </file>
 
@@ -407,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -451,6 +499,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2016,330 +2067,672 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B27" s="14">
+        <v>400</v>
+      </c>
+      <c r="C27" s="14">
+        <v>50</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>200</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>80</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="14">
+        <v>350</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>60</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>400</v>
+      </c>
+      <c r="G28" s="14">
+        <v>8</v>
+      </c>
+      <c r="H28" s="14">
+        <v>70</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="14">
+        <v>430</v>
+      </c>
+      <c r="C29" s="14">
+        <v>60</v>
+      </c>
+      <c r="D29" s="14">
+        <v>30</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>40</v>
+      </c>
+      <c r="D30" s="14">
+        <v>30</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>50</v>
+      </c>
+      <c r="D31" s="14">
+        <v>20</v>
+      </c>
+      <c r="E31" s="14">
+        <v>20</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>60</v>
+      </c>
+      <c r="E32" s="14">
+        <v>30</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>60</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>45</v>
+      </c>
+      <c r="D33" s="14">
+        <v>20</v>
+      </c>
+      <c r="E33" s="14">
+        <v>20</v>
+      </c>
+      <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6</v>
+      </c>
+      <c r="H33" s="14">
+        <v>120</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>925</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>515</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>0</v>
+      </c>
+      <c r="E34" s="14">
+        <v>0</v>
+      </c>
+      <c r="F34" s="14">
+        <v>200</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="14">
+        <v>360</v>
+      </c>
+      <c r="C35" s="14">
+        <v>40</v>
+      </c>
+      <c r="D35" s="14">
+        <v>30</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>400</v>
+      </c>
+      <c r="G35" s="14">
+        <v>8</v>
+      </c>
+      <c r="H35" s="14">
+        <v>60</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B36" s="14">
+        <v>480</v>
+      </c>
+      <c r="C36" s="14">
+        <v>60</v>
+      </c>
+      <c r="D36" s="14">
+        <v>50</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B37" s="21">
+        <v>390</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>30</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>120</v>
+      </c>
+      <c r="I37" s="15">
+        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <v>790</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" si="0"/>
+        <v>650</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B38" s="14">
+        <v>480</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>0</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>300</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B39" s="14">
+        <v>240</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>200</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>150</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B40" s="14">
+        <v>320</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>40</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>300</v>
+      </c>
+      <c r="G40" s="14">
+        <v>6</v>
+      </c>
+      <c r="H40" s="14">
+        <v>120</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
+      <c r="A41" s="13">
+        <v>46287</v>
+      </c>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
+      <c r="F41" s="14">
+        <v>200</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
       <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="I41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>200</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1240</v>
       </c>
       <c r="K41" s="16"/>
       <c r="L41" s="16"/>
@@ -10295,6 +10688,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>